--- a/Sep_2026/Daily Sale/19-09-26/Rainbow Key_Account.xlsx
+++ b/Sep_2026/Daily Sale/19-09-26/Rainbow Key_Account.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08BF2B5-CD13-43DB-BB8C-7F401B9448FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACC021D-91B9-416C-8031-88A168D40952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="594" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -1587,9 +1587,6 @@
     <t>NTN #: 3344916-3</t>
   </si>
   <si>
-    <t>Invoice No # :48915616</t>
-  </si>
-  <si>
     <t>Invoice No # :4512348</t>
   </si>
   <si>
@@ -1621,6 +1618,9 @@
   </si>
   <si>
     <t>Address:EME</t>
+  </si>
+  <si>
+    <t>Invoice No # : 00015</t>
   </si>
 </sst>
 </file>
@@ -7045,6 +7045,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:XFD38"/>
   <sheetFormatPr defaultColWidth="29.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -7208,7 +7211,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -8432,7 +8435,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -53750,7 +53753,7 @@
       </c>
       <c r="K7" s="286">
         <f>+'1'!K16+'2'!K16+'3'!K16+'4'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16+'11'!K16+'12'!K16+'13'!K16+'14'!K16+'15'!K16+'16'!K16+'17'!K16+'18'!K16+'19'!K16+'20'!K16+'21'!K16+'22'!K16+'23'!K16+'24'!K16+'25'!K16+'26'!K16+'27'!K16+'28'!K16+'29'!K16+'30'!K16</f>
-        <v>293.79000000000002</v>
+        <v>367.23750000000001</v>
       </c>
       <c r="L7" s="286">
         <f>+'1'!L16+'2'!L16+'3'!L16+'4'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16+'11'!L16+'12'!L16+'13'!L16+'14'!L16+'15'!L16+'16'!L16+'17'!L16+'18'!L16+'19'!L16+'20'!L16+'21'!L16+'22'!L16+'23'!L16+'24'!L16+'25'!L16+'26'!L16+'27'!L16+'28'!L16+'29'!L16+'30'!L16</f>
@@ -53758,7 +53761,7 @@
       </c>
       <c r="M7" s="229">
         <f>I7-SUM(J7:L7)</f>
-        <v>8729.76</v>
+        <v>8656.3125</v>
       </c>
       <c r="N7" s="286">
         <f>+'1'!N16+'2'!N16+'3'!N16+'4'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16+'11'!N16+'12'!N16+'13'!N16+'14'!N16+'15'!N16+'16'!N16+'17'!N16+'18'!N16+'19'!N16+'20'!N16+'21'!N16+'22'!N16+'23'!N16+'24'!N16+'25'!N16+'26'!N16+'27'!N16+'28'!N16+'29'!N16+'30'!N16</f>
@@ -53766,11 +53769,11 @@
       </c>
       <c r="O7" s="286">
         <f>+'1'!O16+'2'!O16+'3'!O16+'4'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16+'11'!O16+'12'!O16+'13'!O16+'14'!O16+'15'!O16+'16'!O16+'17'!O16+'18'!O16+'19'!O16+'20'!O16+'21'!O16+'22'!O16+'23'!O16+'24'!O16+'25'!O16+'26'!O16+'27'!O16+'28'!O16+'29'!O16+'30'!O16</f>
-        <v>53.564054237288133</v>
+        <v>53.196816737288131</v>
       </c>
       <c r="P7" s="118">
         <f>M7+N7+O7</f>
-        <v>10766.374901694913</v>
+        <v>10692.560164194916</v>
       </c>
       <c r="Q7" s="142"/>
       <c r="R7" s="299">
@@ -53782,7 +53785,7 @@
       </c>
       <c r="T7" s="301">
         <f>+'5'!P35</f>
-        <v>16677.487081016952</v>
+        <v>16121.039686016951</v>
       </c>
       <c r="XEX7" t="s">
         <v>107</v>
@@ -53909,7 +53912,7 @@
       </c>
       <c r="K9" s="286">
         <f>+'1'!K18+'2'!K18+'3'!K18+'4'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18+'11'!K18+'12'!K18+'13'!K18+'14'!K18+'15'!K18+'16'!K18+'17'!K18+'18'!K18+'19'!K18+'20'!K18+'21'!K18+'22'!K18+'23'!K18+'24'!K18+'25'!K18+'26'!K18+'27'!K18+'28'!K18+'29'!K18+'30'!K18</f>
-        <v>1028.2650000000001</v>
+        <v>1101.7125000000001</v>
       </c>
       <c r="L9" s="286">
         <f>+'1'!L18+'2'!L18+'3'!L18+'4'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18+'11'!L18+'12'!L18+'13'!L18+'14'!L18+'15'!L18+'16'!L18+'17'!L18+'18'!L18+'19'!L18+'20'!L18+'21'!L18+'22'!L18+'23'!L18+'24'!L18+'25'!L18+'26'!L18+'27'!L18+'28'!L18+'29'!L18+'30'!L18</f>
@@ -53917,7 +53920,7 @@
       </c>
       <c r="M9" s="230">
         <f t="shared" si="1"/>
-        <v>26042.384999999998</v>
+        <v>25968.9375</v>
       </c>
       <c r="N9" s="286">
         <f>+'1'!N18+'2'!N18+'3'!N18+'4'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18+'11'!N18+'12'!N18+'13'!N18+'14'!N18+'15'!N18+'16'!N18+'17'!N18+'18'!N18+'19'!N18+'20'!N18+'21'!N18+'22'!N18+'23'!N18+'24'!N18+'25'!N18+'26'!N18+'27'!N18+'28'!N18+'29'!N18+'30'!N18</f>
@@ -53925,11 +53928,11 @@
       </c>
       <c r="O9" s="286">
         <f>+'1'!O18+'2'!O18+'3'!O18+'4'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18+'11'!O18+'12'!O18+'13'!O18+'14'!O18+'15'!O18+'16'!O18+'17'!O18+'18'!O18+'19'!O18+'20'!O18+'21'!O18+'22'!O18+'23'!O18+'24'!O18+'25'!O18+'26'!O18+'27'!O18+'28'!O18+'29'!O18+'30'!O18</f>
-        <v>159.95768771186439</v>
+        <v>159.59045021186438</v>
       </c>
       <c r="P9" s="119">
         <f t="shared" si="2"/>
-        <v>32151.49523008474</v>
+        <v>32077.680492584743</v>
       </c>
       <c r="R9" s="299">
         <v>7</v>
@@ -53985,7 +53988,7 @@
       </c>
       <c r="K10" s="286">
         <f>+'1'!K19+'2'!K19+'3'!K19+'4'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19+'11'!K19+'12'!K19+'13'!K19+'14'!K19+'15'!K19+'16'!K19+'17'!K19+'18'!K19+'19'!K19+'20'!K19+'21'!K19+'22'!K19+'23'!K19+'24'!K19+'25'!K19+'26'!K19+'27'!K19+'28'!K19+'29'!K19+'30'!K19</f>
-        <v>711.87200000000007</v>
+        <v>813.5680000000001</v>
       </c>
       <c r="L10" s="286">
         <f>+'1'!L19+'2'!L19+'3'!L19+'4'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19+'11'!L19+'12'!L19+'13'!L19+'14'!L19+'15'!L19+'16'!L19+'17'!L19+'18'!L19+'19'!L19+'20'!L19+'21'!L19+'22'!L19+'23'!L19+'24'!L19+'25'!L19+'26'!L19+'27'!L19+'28'!L19+'29'!L19+'30'!L19</f>
@@ -53993,7 +53996,7 @@
       </c>
       <c r="M10" s="230">
         <f t="shared" si="1"/>
-        <v>19278.655999999999</v>
+        <v>19176.96</v>
       </c>
       <c r="N10" s="286">
         <f>+'1'!N19+'2'!N19+'3'!N19+'4'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19+'11'!N19+'12'!N19+'13'!N19+'14'!N19+'15'!N19+'16'!N19+'17'!N19+'18'!N19+'19'!N19+'20'!N19+'21'!N19+'22'!N19+'23'!N19+'24'!N19+'25'!N19+'26'!N19+'27'!N19+'28'!N19+'29'!N19+'30'!N19</f>
@@ -54001,11 +54004,11 @@
       </c>
       <c r="O10" s="286">
         <f>+'1'!O19+'2'!O19+'3'!O19+'4'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19+'11'!O19+'12'!O19+'13'!O19+'14'!O19+'15'!O19+'16'!O19+'17'!O19+'18'!O19+'19'!O19+'20'!O19+'21'!O19+'22'!O19+'23'!O19+'24'!O19+'25'!O19+'26'!O19+'27'!O19+'28'!O19+'29'!O19+'30'!O19</f>
-        <v>118.35938169491524</v>
+        <v>117.85090169491525</v>
       </c>
       <c r="P10" s="119">
         <f t="shared" si="2"/>
-        <v>23790.235720677963</v>
+        <v>23688.031240677963</v>
       </c>
       <c r="R10" s="299">
         <v>8</v>
@@ -54061,7 +54064,7 @@
       </c>
       <c r="K11" s="286">
         <f>+'1'!K20+'2'!K20+'3'!K20+'4'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20+'11'!K20+'12'!K20+'13'!K20+'14'!K20+'15'!K20+'16'!K20+'17'!K20+'18'!K20+'19'!K20+'20'!K20+'21'!K20+'22'!K20+'23'!K20+'24'!K20+'25'!K20+'26'!K20+'27'!K20+'28'!K20+'29'!K20+'30'!K20</f>
-        <v>813.5680000000001</v>
+        <v>915.26400000000012</v>
       </c>
       <c r="L11" s="286">
         <f>+'1'!L20+'2'!L20+'3'!L20+'4'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20+'11'!L20+'12'!L20+'13'!L20+'14'!L20+'15'!L20+'16'!L20+'17'!L20+'18'!L20+'19'!L20+'20'!L20+'21'!L20+'22'!L20+'23'!L20+'24'!L20+'25'!L20+'26'!L20+'27'!L20+'28'!L20+'29'!L20+'30'!L20</f>
@@ -54069,7 +54072,7 @@
       </c>
       <c r="M11" s="230">
         <f t="shared" si="1"/>
-        <v>21675.776000000002</v>
+        <v>21574.080000000002</v>
       </c>
       <c r="N11" s="286">
         <f>+'1'!N20+'2'!N20+'3'!N20+'4'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20+'11'!N20+'12'!N20+'13'!N20+'14'!N20+'15'!N20+'16'!N20+'17'!N20+'18'!N20+'19'!N20+'20'!N20+'21'!N20+'22'!N20+'23'!N20+'24'!N20+'25'!N20+'26'!N20+'27'!N20+'28'!N20+'29'!N20+'30'!N20</f>
@@ -54077,11 +54080,11 @@
       </c>
       <c r="O11" s="286">
         <f>+'1'!O20+'2'!O20+'3'!O20+'4'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20+'11'!O20+'12'!O20+'13'!O20+'14'!O20+'15'!O20+'16'!O20+'17'!O20+'18'!O20+'19'!O20+'20'!O20+'21'!O20+'22'!O20+'23'!O20+'24'!O20+'25'!O20+'26'!O20+'27'!O20+'28'!O20+'29'!O20+'30'!O20</f>
-        <v>133.09074440677966</v>
+        <v>132.58226440677964</v>
       </c>
       <c r="P11" s="119">
         <f t="shared" si="2"/>
-        <v>26751.239625762712</v>
+        <v>26649.035145762715</v>
       </c>
       <c r="R11" s="299">
         <v>9</v>
@@ -54137,7 +54140,7 @@
       </c>
       <c r="K12" s="286">
         <f>+'1'!K21+'2'!K21+'3'!K21+'4'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21+'11'!K21+'12'!K21+'13'!K21+'14'!K21+'15'!K21+'16'!K21+'17'!K21+'18'!K21+'19'!K21+'20'!K21+'21'!K21+'22'!K21+'23'!K21+'24'!K21+'25'!K21+'26'!K21+'27'!K21+'28'!K21+'29'!K21+'30'!K21</f>
-        <v>2237.3119999999999</v>
+        <v>2440.7039999999997</v>
       </c>
       <c r="L12" s="286">
         <f>+'1'!L21+'2'!L21+'3'!L21+'4'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21+'11'!L21+'12'!L21+'13'!L21+'14'!L21+'15'!L21+'16'!L21+'17'!L21+'18'!L21+'19'!L21+'20'!L21+'21'!L21+'22'!L21+'23'!L21+'24'!L21+'25'!L21+'26'!L21+'27'!L21+'28'!L21+'29'!L21+'30'!L21</f>
@@ -54145,7 +54148,7 @@
       </c>
       <c r="M12" s="230">
         <f t="shared" si="1"/>
-        <v>57734.271999999997</v>
+        <v>57530.879999999997</v>
       </c>
       <c r="N12" s="286">
         <f>+'1'!N21+'2'!N21+'3'!N21+'4'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21+'11'!N21+'12'!N21+'13'!N21+'14'!N21+'15'!N21+'16'!N21+'17'!N21+'18'!N21+'19'!N21+'20'!N21+'21'!N21+'22'!N21+'23'!N21+'24'!N21+'25'!N21+'26'!N21+'27'!N21+'28'!N21+'29'!N21+'30'!N21</f>
@@ -54153,11 +54156,11 @@
       </c>
       <c r="O12" s="286">
         <f>+'1'!O21+'2'!O21+'3'!O21+'4'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21+'11'!O21+'12'!O21+'13'!O21+'14'!O21+'15'!O21+'16'!O21+'17'!O21+'18'!O21+'19'!O21+'20'!O21+'21'!O21+'22'!O21+'23'!O21+'24'!O21+'25'!O21+'26'!O21+'27'!O21+'28'!O21+'29'!O21+'30'!O21</f>
-        <v>354.56966508474574</v>
+        <v>353.5527050847457</v>
       </c>
       <c r="P12" s="119">
         <f t="shared" si="2"/>
-        <v>71268.502682033897</v>
+        <v>71064.093722033896</v>
       </c>
       <c r="R12" s="299">
         <v>10</v>
@@ -54429,7 +54432,7 @@
       </c>
       <c r="K16" s="275">
         <f t="shared" si="3"/>
-        <v>5452.0445</v>
+        <v>6005.7235000000001</v>
       </c>
       <c r="L16" s="276">
         <f t="shared" si="3"/>
@@ -54437,7 +54440,7 @@
       </c>
       <c r="M16" s="232">
         <f t="shared" si="3"/>
-        <v>142117.16149999999</v>
+        <v>141563.48250000001</v>
       </c>
       <c r="N16" s="233">
         <f>SUM(N7:N15)</f>
@@ -54445,11 +54448,11 @@
       </c>
       <c r="O16" s="101">
         <f>SUM(O7:O15)</f>
-        <v>872.73834987288137</v>
+        <v>869.96995487288109</v>
       </c>
       <c r="P16" s="234">
         <f>SUM(P7:P15)</f>
-        <v>175420.40832444915</v>
+        <v>174863.96092944912</v>
       </c>
       <c r="R16" s="299">
         <v>14</v>
@@ -54596,7 +54599,7 @@
       <c r="O21" s="376"/>
       <c r="P21" s="140">
         <f>+K16+L16</f>
-        <v>5452.0445</v>
+        <v>6005.7235000000001</v>
       </c>
       <c r="R21" s="299">
         <v>19</v>
@@ -54629,7 +54632,7 @@
       <c r="O22" s="376"/>
       <c r="P22" s="140">
         <f>P19-P20-P21</f>
-        <v>142117.16150000002</v>
+        <v>141563.48250000001</v>
       </c>
       <c r="R22" s="299">
         <v>20</v>
@@ -54697,7 +54700,7 @@
       <c r="O24" s="378"/>
       <c r="P24" s="140">
         <f>P22+P23</f>
-        <v>174547.66997457627</v>
+        <v>173993.99097457627</v>
       </c>
       <c r="R24" s="299">
         <v>22</v>
@@ -54733,7 +54736,7 @@
       </c>
       <c r="P25" s="140">
         <f>+O16</f>
-        <v>872.73834987288137</v>
+        <v>869.96995487288109</v>
       </c>
       <c r="R25" s="299">
         <v>23</v>
@@ -54754,7 +54757,7 @@
       <c r="O26" s="336"/>
       <c r="P26" s="297">
         <f>+P24+P25</f>
-        <v>175420.40832444915</v>
+        <v>174863.96092944915</v>
       </c>
       <c r="R26" s="299">
         <v>24</v>
@@ -54868,7 +54871,7 @@
       </c>
       <c r="T33" s="304">
         <f>SUM(T3:T32)</f>
-        <v>175420.40832444912</v>
+        <v>174863.96092944912</v>
       </c>
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.35">
@@ -54950,7 +54953,7 @@
     <col min="8" max="8" width="5.453125" customWidth="1"/>
     <col min="9" max="9" width="8.54296875" customWidth="1"/>
     <col min="10" max="10" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
     <col min="13" max="13" width="8" customWidth="1"/>
     <col min="14" max="14" width="9.1796875" style="61" bestFit="1" customWidth="1"/>
@@ -54978,7 +54981,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
       <c r="K3" s="360" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="L3" s="360"/>
       <c r="M3" s="360"/>
@@ -55072,7 +55075,7 @@
     </row>
     <row r="7" spans="1:22 16383:16384" s="87" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="360" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B7" s="360"/>
       <c r="C7" s="360"/>
@@ -55101,7 +55104,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -56388,7 +56391,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
       <c r="K3" s="360" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="L3" s="360"/>
       <c r="M3" s="360"/>
@@ -56511,7 +56514,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -57798,7 +57801,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
       <c r="K3" s="360" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L3" s="360"/>
       <c r="M3" s="360"/>
@@ -57921,7 +57924,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -59206,7 +59209,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
       <c r="K3" s="360" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="L3" s="360"/>
       <c r="M3" s="360"/>
@@ -59329,7 +59332,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -60631,7 +60634,7 @@
       <c r="F3" s="85"/>
       <c r="G3" s="1"/>
       <c r="K3" s="360" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="L3" s="360"/>
       <c r="M3" s="360"/>
@@ -60661,7 +60664,7 @@
       <c r="L4" s="360"/>
       <c r="M4" s="360"/>
       <c r="N4" s="390">
-        <v>46272</v>
+        <v>46283</v>
       </c>
       <c r="O4" s="390"/>
       <c r="P4" s="390"/>
@@ -60689,7 +60692,7 @@
       <c r="M5" s="360"/>
       <c r="N5" s="390">
         <f>N4-1</f>
-        <v>46271</v>
+        <v>46282</v>
       </c>
       <c r="O5" s="359"/>
       <c r="P5" s="359"/>
@@ -60754,7 +60757,7 @@
     </row>
     <row r="8" spans="1:22 16383:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="386" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B8" s="386"/>
       <c r="C8" s="386"/>
@@ -61020,7 +61023,7 @@
       </c>
       <c r="K16" s="127">
         <f>$I16*T16</f>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L16" s="118">
         <f>$I16*U16</f>
@@ -61028,7 +61031,7 @@
       </c>
       <c r="M16" s="229">
         <f>I16-SUM(J16:L16)</f>
-        <v>1804.71</v>
+        <v>1731.2625</v>
       </c>
       <c r="N16" s="248">
         <f>+(G16*D16+H16)*V16</f>
@@ -61036,17 +61039,19 @@
       </c>
       <c r="O16" s="238">
         <f>(N16+M16)*$O$15</f>
-        <v>11.006600847457626</v>
+        <v>10.639363347457627</v>
       </c>
       <c r="P16" s="118">
         <f>M16+N16+O16</f>
-        <v>2212.3267703389829</v>
+        <v>2138.512032838983</v>
       </c>
       <c r="Q16" s="142"/>
       <c r="S16" s="269">
         <v>0.14000000000000001</v>
       </c>
-      <c r="T16" s="270"/>
+      <c r="T16" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U16" s="269"/>
       <c r="V16" s="142">
         <f>+E16-E16/1.18</f>
@@ -61118,7 +61123,9 @@
         <f>+S16</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="T17" s="270"/>
+      <c r="T17" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U17" s="269"/>
       <c r="V17" s="142">
         <f t="shared" ref="V17:V24" si="6">+E17-E17/1.18</f>
@@ -61166,7 +61173,7 @@
       </c>
       <c r="K18" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L18" s="119">
         <f t="shared" si="1"/>
@@ -61174,7 +61181,7 @@
       </c>
       <c r="M18" s="230">
         <f t="shared" si="2"/>
-        <v>1804.71</v>
+        <v>1731.2625</v>
       </c>
       <c r="N18" s="277">
         <f t="shared" si="3"/>
@@ -61182,17 +61189,19 @@
       </c>
       <c r="O18" s="239">
         <f t="shared" si="4"/>
-        <v>11.006600847457626</v>
+        <v>10.639363347457627</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="5"/>
-        <v>2212.3267703389829</v>
+        <v>2138.512032838983</v>
       </c>
       <c r="S18" s="269">
         <f>+S17</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="T18" s="270"/>
+      <c r="T18" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U18" s="269"/>
       <c r="V18" s="142">
         <f t="shared" si="6"/>
@@ -61237,7 +61246,7 @@
       </c>
       <c r="K19" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L19" s="119">
         <f t="shared" si="1"/>
@@ -61245,7 +61254,7 @@
       </c>
       <c r="M19" s="230">
         <f t="shared" si="2"/>
-        <v>2498.8159999999998</v>
+        <v>2397.12</v>
       </c>
       <c r="N19" s="277">
         <f t="shared" si="3"/>
@@ -61253,17 +61262,19 @@
       </c>
       <c r="O19" s="239">
         <f t="shared" si="4"/>
-        <v>15.239842711864405</v>
+        <v>14.731362711864406</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="5"/>
-        <v>3063.2083850847453</v>
+        <v>2961.0039050847454</v>
       </c>
       <c r="S19" s="269">
         <f>+S18</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="T19" s="270"/>
+      <c r="T19" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U19" s="269"/>
       <c r="V19" s="142">
         <f t="shared" si="6"/>
@@ -61308,7 +61319,7 @@
       </c>
       <c r="K20" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L20" s="119">
         <f t="shared" si="1"/>
@@ -61316,7 +61327,7 @@
       </c>
       <c r="M20" s="230">
         <f t="shared" si="2"/>
-        <v>2498.8159999999998</v>
+        <v>2397.12</v>
       </c>
       <c r="N20" s="277">
         <f t="shared" si="3"/>
@@ -61324,21 +61335,23 @@
       </c>
       <c r="O20" s="239">
         <f t="shared" si="4"/>
-        <v>15.239842711864405</v>
+        <v>14.731362711864406</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="5"/>
-        <v>3063.2083850847453</v>
+        <v>2961.0039050847454</v>
       </c>
       <c r="R20">
         <f>P20/21</f>
-        <v>145.86706595641644</v>
+        <v>141.00018595641646</v>
       </c>
       <c r="S20" s="269">
         <f>+S19</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="T20" s="270"/>
+      <c r="T20" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U20" s="269"/>
       <c r="V20" s="142">
         <f t="shared" si="6"/>
@@ -61383,7 +61396,7 @@
       </c>
       <c r="K21" s="128">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>203.39200000000002</v>
       </c>
       <c r="L21" s="119">
         <f t="shared" si="1"/>
@@ -61391,7 +61404,7 @@
       </c>
       <c r="M21" s="230">
         <f t="shared" si="2"/>
-        <v>4997.6319999999996</v>
+        <v>4794.24</v>
       </c>
       <c r="N21" s="277">
         <f t="shared" si="3"/>
@@ -61399,17 +61412,19 @@
       </c>
       <c r="O21" s="239">
         <f t="shared" si="4"/>
-        <v>30.47968542372881</v>
+        <v>29.462725423728813</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="5"/>
-        <v>6126.4167701694905</v>
+        <v>5922.0078101694908</v>
       </c>
       <c r="S21" s="269">
         <f>+S20</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="T21" s="270"/>
+      <c r="T21" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U21" s="269"/>
       <c r="V21" s="142">
         <f t="shared" si="6"/>
@@ -61477,7 +61492,9 @@
       <c r="S22" s="269">
         <v>0.05</v>
       </c>
-      <c r="T22" s="270"/>
+      <c r="T22" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U22" s="270">
         <v>5.0999999999999997E-2</v>
       </c>
@@ -61547,7 +61564,9 @@
       <c r="S23" s="269">
         <v>0.05</v>
       </c>
-      <c r="T23" s="270"/>
+      <c r="T23" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U23" s="270">
         <f>+U22</f>
         <v>5.0999999999999997E-2</v>
@@ -61618,7 +61637,9 @@
       <c r="S24" s="269">
         <v>0.05</v>
       </c>
-      <c r="T24" s="270"/>
+      <c r="T24" s="270">
+        <v>3.5000000000000003E-2</v>
+      </c>
       <c r="U24" s="270">
         <f>+U23</f>
         <v>5.0999999999999997E-2</v>
@@ -61658,7 +61679,7 @@
       </c>
       <c r="K25" s="275">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>553.67900000000009</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" si="7"/>
@@ -61666,7 +61687,7 @@
       </c>
       <c r="M25" s="232">
         <f t="shared" si="7"/>
-        <v>13604.683999999999</v>
+        <v>13051.004999999999</v>
       </c>
       <c r="N25" s="233">
         <f>SUM(N16:N24)</f>
@@ -61674,11 +61695,11 @@
       </c>
       <c r="O25" s="101">
         <f>SUM(O16:O24)</f>
-        <v>82.972572542372873</v>
+        <v>80.204177542372875</v>
       </c>
       <c r="P25" s="234">
         <f>SUM(P16:P24)</f>
-        <v>16677.487081016945</v>
+        <v>16121.039686016948</v>
       </c>
     </row>
     <row r="26" spans="1:22 16384:16384" x14ac:dyDescent="0.35">
@@ -61770,7 +61791,7 @@
       <c r="O30" s="376"/>
       <c r="P30" s="140">
         <f>+K25+L25</f>
-        <v>0</v>
+        <v>553.67900000000009</v>
       </c>
     </row>
     <row r="31" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61792,7 +61813,7 @@
       <c r="O31" s="376"/>
       <c r="P31" s="140">
         <f>P28-P29-P30</f>
-        <v>13604.684000000001</v>
+        <v>13051.005000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -61838,7 +61859,7 @@
       <c r="O33" s="378"/>
       <c r="P33" s="140">
         <f>P31+P32</f>
-        <v>16594.514508474578</v>
+        <v>16040.835508474578</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -61863,7 +61884,7 @@
       </c>
       <c r="P34" s="140">
         <f>O34*P33</f>
-        <v>82.972572542372887</v>
+        <v>80.204177542372889</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -61873,7 +61894,7 @@
       <c r="O35" s="336"/>
       <c r="P35" s="297">
         <f>+P33+P34</f>
-        <v>16677.487081016952</v>
+        <v>16121.039686016951</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
